--- a/curation/draft/package16/R16_BC_LB_New.xlsx
+++ b/curation/draft/package16/R16_BC_LB_New.xlsx
@@ -2,24 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAC3C85-D2E6-4388-9DF0-9752D7F57911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F602DD5-331F-436E-9F42-83CDDEE25E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="915" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F590C486-C613-40E0-BF06-47BB8CB37E44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F590C486-C613-40E0-BF06-47BB8CB37E44}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_LB_Edits" sheetId="2" r:id="rId1"/>
     <sheet name="SDTM_LB_Edits" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SDTM_LB_Edits!$A$1:$AF$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SDTM_LB_Edits!$A$1:$AF$40</definedName>
   </definedNames>
-  <calcPr calcId="191028" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="157">
   <si>
     <t>package_date</t>
   </si>
@@ -78,6 +78,9 @@
     <t>code</t>
   </si>
   <si>
+    <t>R16</t>
+  </si>
+  <si>
     <t>dec_id</t>
   </si>
   <si>
@@ -93,85 +96,340 @@
     <t>example_set</t>
   </si>
   <si>
-    <t>R16</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>sdtmig_start_version</t>
+  </si>
+  <si>
+    <t>sdtmig_end_version</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>vlm_source</t>
+  </si>
+  <si>
+    <t>vlm_group_id</t>
+  </si>
+  <si>
+    <t>sdtm_variable</t>
+  </si>
+  <si>
+    <t>nsv_flag</t>
+  </si>
+  <si>
+    <t>codelist</t>
+  </si>
+  <si>
+    <t>codelist_submission_value</t>
+  </si>
+  <si>
+    <t>subset_codelist</t>
+  </si>
+  <si>
+    <t>value_list</t>
+  </si>
+  <si>
+    <t>assigned_term</t>
+  </si>
+  <si>
+    <t>assigned_value</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>subject</t>
+  </si>
+  <si>
+    <t>linking_phrase</t>
+  </si>
+  <si>
+    <t>predicate_term</t>
+  </si>
+  <si>
+    <t>object</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>format</t>
+  </si>
+  <si>
+    <t>significant_digits</t>
+  </si>
+  <si>
+    <t>mandatory_variable</t>
+  </si>
+  <si>
+    <t>mandatory_value</t>
+  </si>
+  <si>
+    <t>origin_type</t>
+  </si>
+  <si>
+    <t>origin_source</t>
+  </si>
+  <si>
+    <t>comparator</t>
+  </si>
+  <si>
+    <t>vlm_target</t>
+  </si>
+  <si>
+    <t>Quantitative</t>
+  </si>
+  <si>
+    <t>C70856</t>
+  </si>
+  <si>
+    <t>Observation Result</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>C82515</t>
+  </si>
+  <si>
+    <t>Collection Date Time</t>
+  </si>
+  <si>
+    <t>C93566</t>
+  </si>
+  <si>
+    <t>Fasting Status Indicator</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>C70713</t>
+  </si>
+  <si>
+    <t>Biospecimen Type</t>
+  </si>
+  <si>
+    <t>Sodium Excretion Rate</t>
+  </si>
+  <si>
+    <t>C150823</t>
+  </si>
+  <si>
+    <t>SODMEXR</t>
+  </si>
+  <si>
+    <t>A determination of the amount of sodium being excreted in a biological specimen over a defined period of time.</t>
+  </si>
+  <si>
+    <t>C85534</t>
   </si>
   <si>
     <t>Excretion Rate</t>
   </si>
   <si>
-    <t>C85534</t>
-  </si>
-  <si>
     <t>Laboratory Tests;Biological Clearance Rates;Clearance Rates;Excreation Rates</t>
   </si>
   <si>
     <t>The speed relative to time that an exogenous compound is removed from a body system.</t>
   </si>
   <si>
-    <t>Sodium Excretion Rate</t>
-  </si>
-  <si>
-    <t>C150823</t>
-  </si>
-  <si>
-    <t>SODMEXR</t>
-  </si>
-  <si>
-    <t>Quantitative</t>
-  </si>
-  <si>
-    <t>A determination of the amount of sodium being excreted in a biological specimen over a defined period of time.</t>
+    <t>Unit of Flow Rate</t>
   </si>
   <si>
     <t>C48567</t>
   </si>
   <si>
-    <t>Unit of Flow Rate</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>C93566</t>
-  </si>
-  <si>
-    <t>Fasting Status Indicator</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>C70856</t>
-  </si>
-  <si>
-    <t>Observation Result</t>
-  </si>
-  <si>
-    <t>decimal</t>
-  </si>
-  <si>
-    <t>C70713</t>
-  </si>
-  <si>
-    <t>Biospecimen Type</t>
+    <t>Urine;Serum or Plasma</t>
   </si>
   <si>
     <t>Urine;Serum or Plasma;Stool</t>
   </si>
   <si>
-    <t>C82515</t>
-  </si>
-  <si>
-    <t>Collection Date Time</t>
-  </si>
-  <si>
-    <t>datetime</t>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>LB.LBTESTCD</t>
+  </si>
+  <si>
+    <t>LBTESTCD</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>C65047</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>is the code for the value in</t>
+  </si>
+  <si>
+    <t>IS_DECODED_BY</t>
+  </si>
+  <si>
+    <t>LBTEST</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>C67154</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t>decodes the value in</t>
+  </si>
+  <si>
+    <t>DECODES</t>
+  </si>
+  <si>
+    <t>LBCAT</t>
+  </si>
+  <si>
+    <t>CHEMISTRY</t>
+  </si>
+  <si>
+    <t>groups values in</t>
+  </si>
+  <si>
+    <t>GROUPS</t>
+  </si>
+  <si>
+    <t>LBORRES</t>
+  </si>
+  <si>
+    <t>is the result of the test in</t>
+  </si>
+  <si>
+    <t>IS_RESULT_OF</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>12.4</t>
+  </si>
+  <si>
+    <t>Collected</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>LBORRESU</t>
+  </si>
+  <si>
+    <t>C71620</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>is the unit for the value in</t>
+  </si>
+  <si>
+    <t>IS_UNIT_FOR</t>
+  </si>
+  <si>
+    <t>LBSTRESC</t>
+  </si>
+  <si>
+    <t>LBSTRESN</t>
+  </si>
+  <si>
+    <t>LBSTRESU</t>
+  </si>
+  <si>
+    <t>LBLOINC</t>
+  </si>
+  <si>
+    <t>identifies an observation described by</t>
+  </si>
+  <si>
+    <t>IDENTIFIES_OBSERVATION</t>
+  </si>
+  <si>
+    <t>LBSPEC</t>
+  </si>
+  <si>
+    <t>C78734</t>
+  </si>
+  <si>
+    <t>SPECTYPE</t>
+  </si>
+  <si>
+    <t>C13283</t>
+  </si>
+  <si>
+    <t>URINE</t>
+  </si>
+  <si>
+    <t>is the specimen tested in</t>
+  </si>
+  <si>
+    <t>IS_SPECIMEN_TESTED_IN</t>
+  </si>
+  <si>
+    <t>LBFAST</t>
+  </si>
+  <si>
+    <t>C66742</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>NY_NY</t>
+  </si>
+  <si>
+    <t>N;Y</t>
+  </si>
+  <si>
+    <t>is the subject's fasting status during the performance of the test in</t>
+  </si>
+  <si>
+    <t>IS_SUBJECT_STATE_FOR</t>
+  </si>
+  <si>
+    <t>LBDTC</t>
+  </si>
+  <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>is the date of occurrence for</t>
+  </si>
+  <si>
+    <t>IS_TIMING_FOR</t>
+  </si>
+  <si>
+    <t>Laboratory Test End Date Time</t>
   </si>
   <si>
     <t>C83308</t>
   </si>
   <si>
-    <t>Laboratory Test End Date Time</t>
+    <t>LBENDTC</t>
+  </si>
+  <si>
+    <t>is the end date for</t>
   </si>
   <si>
     <t>Sodium Clearance Measurement</t>
@@ -180,331 +438,70 @@
     <t>C106568</t>
   </si>
   <si>
+    <t>NACLR;Sodium Clearance</t>
+  </si>
+  <si>
+    <t>The determination of the amount of the sodium clearance in a sample.</t>
+  </si>
+  <si>
+    <t>Laboratory Tests;Chemistry Tests;Clearance Rates</t>
+  </si>
+  <si>
+    <t>Sodium Clearance in Urine</t>
+  </si>
+  <si>
     <t>C49237</t>
   </si>
   <si>
-    <t>Laboratory Tests;Chemistry Tests;Clearance Rates</t>
-  </si>
-  <si>
-    <t>NACLR;Sodium Clearance</t>
-  </si>
-  <si>
-    <t>The determination of the amount of the sodium clearance in a sample.</t>
+    <t>NACLR</t>
+  </si>
+  <si>
+    <t>Sodium Clearance</t>
   </si>
   <si>
     <t>ml/min;mL/s</t>
   </si>
   <si>
-    <t>Urine;Serum or Plasma</t>
+    <t>mL/s</t>
+  </si>
+  <si>
+    <t>C69073</t>
+  </si>
+  <si>
+    <t>SODEXRURIN</t>
+  </si>
+  <si>
+    <t>Sodium Excretion Rate in Urine</t>
+  </si>
+  <si>
+    <t>C85723</t>
+  </si>
+  <si>
+    <t>mmol/s</t>
+  </si>
+  <si>
+    <t>mmol/day;mmol/s</t>
+  </si>
+  <si>
+    <t>C25747</t>
+  </si>
+  <si>
+    <t>C64547</t>
+  </si>
+  <si>
+    <t>CREATCLR</t>
+  </si>
+  <si>
+    <t>The determination of the clearance of endogenous creatinine, used for evaluating the glomerular filtration rate.</t>
+  </si>
+  <si>
+    <t>Laboratory Tests;Chemistry Tests;Clearance Rates;Creatinine Measurements</t>
+  </si>
+  <si>
+    <t>Creatinine Clearance in Urine</t>
   </si>
   <si>
     <t>Creatinine Clearance</t>
-  </si>
-  <si>
-    <t>C25747</t>
-  </si>
-  <si>
-    <t>C64547</t>
-  </si>
-  <si>
-    <t>Laboratory Tests;Chemistry Tests;Clearance Rates;Creatinine Measurements</t>
-  </si>
-  <si>
-    <t>CREATCLR</t>
-  </si>
-  <si>
-    <t>The determination of the clearance of endogenous creatinine, used for evaluating the glomerular filtration rate.</t>
-  </si>
-  <si>
-    <t>sdtmig_start_version</t>
-  </si>
-  <si>
-    <t>sdtmig_end_version</t>
-  </si>
-  <si>
-    <t>domain</t>
-  </si>
-  <si>
-    <t>vlm_source</t>
-  </si>
-  <si>
-    <t>vlm_group_id</t>
-  </si>
-  <si>
-    <t>sdtm_variable</t>
-  </si>
-  <si>
-    <t>nsv_flag</t>
-  </si>
-  <si>
-    <t>codelist</t>
-  </si>
-  <si>
-    <t>codelist_submission_value</t>
-  </si>
-  <si>
-    <t>subset_codelist</t>
-  </si>
-  <si>
-    <t>value_list</t>
-  </si>
-  <si>
-    <t>assigned_term</t>
-  </si>
-  <si>
-    <t>assigned_value</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>subject</t>
-  </si>
-  <si>
-    <t>linking_phrase</t>
-  </si>
-  <si>
-    <t>predicate_term</t>
-  </si>
-  <si>
-    <t>object</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>format</t>
-  </si>
-  <si>
-    <t>significant_digits</t>
-  </si>
-  <si>
-    <t>mandatory_variable</t>
-  </si>
-  <si>
-    <t>mandatory_value</t>
-  </si>
-  <si>
-    <t>origin_type</t>
-  </si>
-  <si>
-    <t>origin_source</t>
-  </si>
-  <si>
-    <t>comparator</t>
-  </si>
-  <si>
-    <t>vlm_target</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>LB</t>
-  </si>
-  <si>
-    <t>LB.LBTESTCD</t>
-  </si>
-  <si>
-    <t>Sodium Clearance in Urine</t>
-  </si>
-  <si>
-    <t>LBTESTCD</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>C65047</t>
-  </si>
-  <si>
-    <t>NACLR</t>
-  </si>
-  <si>
-    <t>Topic</t>
-  </si>
-  <si>
-    <t>is the code for the value in</t>
-  </si>
-  <si>
-    <t>IS_DECODED_BY</t>
-  </si>
-  <si>
-    <t>LBTEST</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>EQ</t>
-  </si>
-  <si>
-    <t>C67154</t>
-  </si>
-  <si>
-    <t>Sodium Clearance</t>
-  </si>
-  <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t>decodes the value in</t>
-  </si>
-  <si>
-    <t>DECODES</t>
-  </si>
-  <si>
-    <t>LBCAT</t>
-  </si>
-  <si>
-    <t>CHEMISTRY</t>
-  </si>
-  <si>
-    <t>groups values in</t>
-  </si>
-  <si>
-    <t>GROUPS</t>
-  </si>
-  <si>
-    <t>LBORRES</t>
-  </si>
-  <si>
-    <t>is the result of the test in</t>
-  </si>
-  <si>
-    <t>IS_RESULT_OF</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>12.4</t>
-  </si>
-  <si>
-    <t>Collected</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>LBORRESU</t>
-  </si>
-  <si>
-    <t>C64567</t>
-  </si>
-  <si>
-    <t>C71620</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>is the unit for the value in</t>
-  </si>
-  <si>
-    <t>IS_UNIT_FOR</t>
-  </si>
-  <si>
-    <t>LBSTRESC</t>
-  </si>
-  <si>
-    <t>LBSTRESN</t>
-  </si>
-  <si>
-    <t>LBSTRESU</t>
-  </si>
-  <si>
-    <t>C69073</t>
-  </si>
-  <si>
-    <t>mL/s</t>
-  </si>
-  <si>
-    <t>LBLOINC</t>
-  </si>
-  <si>
-    <t>identifies an observation described by</t>
-  </si>
-  <si>
-    <t>IDENTIFIES_OBSERVATION</t>
-  </si>
-  <si>
-    <t>LBSPEC</t>
-  </si>
-  <si>
-    <t>C78734</t>
-  </si>
-  <si>
-    <t>SPECTYPE</t>
-  </si>
-  <si>
-    <t>C13283</t>
-  </si>
-  <si>
-    <t>URINE</t>
-  </si>
-  <si>
-    <t>is the specimen tested in</t>
-  </si>
-  <si>
-    <t>IS_SPECIMEN_TESTED_IN</t>
-  </si>
-  <si>
-    <t>LBFAST</t>
-  </si>
-  <si>
-    <t>C66742</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>NY_NY</t>
-  </si>
-  <si>
-    <t>N;Y</t>
-  </si>
-  <si>
-    <t>is the subject's fasting status during the performance of the test in</t>
-  </si>
-  <si>
-    <t>IS_SUBJECT_STATE_FOR</t>
-  </si>
-  <si>
-    <t>LBDTC</t>
-  </si>
-  <si>
-    <t>Timing</t>
-  </si>
-  <si>
-    <t>is the date of occurrence for</t>
-  </si>
-  <si>
-    <t>IS_TIMING_FOR</t>
-  </si>
-  <si>
-    <t>LBENDTC</t>
-  </si>
-  <si>
-    <t>is the end date for</t>
-  </si>
-  <si>
-    <t>SODEXRURIN</t>
-  </si>
-  <si>
-    <t>Sodium Excretion Rate in Urine</t>
-  </si>
-  <si>
-    <t>mmol/day;mmol/s</t>
-  </si>
-  <si>
-    <t>C85723</t>
-  </si>
-  <si>
-    <t>mmol/s</t>
-  </si>
-  <si>
-    <t>Creatinine Clearance in Urine</t>
   </si>
   <si>
     <t>NACLRURIN</t>
@@ -660,14 +657,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1006,7 +1003,7 @@
   <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
@@ -1059,42 +1056,42 @@
         <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="4" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1107,823 +1104,823 @@
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="4"/>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="Q7" s="4"/>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="Q8" s="4"/>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="I10" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="I11" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="4"/>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="I12" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="I13" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="Q13" s="4"/>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="Q14" s="4"/>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Q16" s="4"/>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="Q17" s="4"/>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="Q19" s="4"/>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="Q20" s="4"/>
     </row>
@@ -1973,3039 +1970,3032 @@
   <dimension ref="A1:AF40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" customWidth="1"/>
     <col min="4" max="4" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.42578125" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" customWidth="1"/>
     <col min="17" max="17" width="29.7109375" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" customWidth="1"/>
-    <col min="19" max="19" width="13.7109375" customWidth="1"/>
-    <col min="20" max="20" width="65.5703125" customWidth="1"/>
-    <col min="21" max="21" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="20" max="20" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="8" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:32" s="10" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q1" s="10" t="s">
+      <c r="I1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="X1" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF1" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
+      <c r="O2" s="4"/>
       <c r="P2" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
       <c r="AA2" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
       <c r="AE2" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="O3" s="4"/>
       <c r="P3" s="3" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="O4" s="4"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>106</v>
+        <v>86</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="4"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X5" s="3">
         <v>12</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z5" s="3">
         <v>4</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="N6" s="3"/>
-      <c r="O6" s="3" t="s">
-        <v>50</v>
+      <c r="O6" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="S6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="V6" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="O7" s="4"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X7" s="3">
         <v>12</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z7" s="3">
         <v>4</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC7" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD7" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+      <c r="O8" s="4"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X8" s="3">
         <v>12</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z8" s="3">
         <v>4</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="O9" s="4"/>
       <c r="P9" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="V9" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
+      <c r="O10" s="4"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>127</v>
+        <v>105</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
     </row>
-    <row r="11" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="O11" s="4"/>
       <c r="P11" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AF11" s="3"/>
     </row>
-    <row r="12" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>141</v>
+        <v>115</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
     </row>
-    <row r="13" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
+      <c r="O13" s="4"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>145</v>
+        <v>122</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
     </row>
-    <row r="14" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="O14" s="4"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>148</v>
+        <v>128</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="O15" s="4"/>
       <c r="P15" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB15" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AF15" s="3"/>
     </row>
-    <row r="16" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="O16" s="4"/>
       <c r="P16" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB16" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
     </row>
-    <row r="17" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
+      <c r="O17" s="4"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>106</v>
+        <v>86</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB17" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
     </row>
-    <row r="18" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="O18" s="4"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X18" s="3">
         <v>12</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z18" s="3">
         <v>4</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB18" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD18" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="N19" s="3"/>
-      <c r="O19" s="3" t="s">
-        <v>151</v>
+      <c r="O19" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="S19" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="V19" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB19" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
+      <c r="O20" s="4"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X20" s="3">
         <v>12</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z20" s="3">
         <v>4</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC20" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE20" s="3"/>
       <c r="AF20" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
+      <c r="O21" s="4"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X21" s="3">
         <v>12</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z21" s="3">
         <v>4</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC21" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD21" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE21" s="3"/>
       <c r="AF21" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
+      <c r="O22" s="4"/>
       <c r="P22" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="V22" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB22" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3"/>
       <c r="AF22" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
+      <c r="O23" s="4"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>127</v>
+        <v>105</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AB23" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
     </row>
-    <row r="24" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
+      <c r="O24" s="4"/>
       <c r="P24" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>141</v>
+        <v>115</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AB25" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
+      <c r="O26" s="4"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>145</v>
+        <v>122</v>
+      </c>
+      <c r="T26" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB26" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
+      <c r="O27" s="4"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>148</v>
+        <v>128</v>
+      </c>
+      <c r="T27" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB27" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
-    <row r="28" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
+      <c r="O28" s="4"/>
       <c r="P28" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
+      </c>
+      <c r="T28" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB28" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AF28" s="3"/>
     </row>
-    <row r="29" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
+      <c r="O29" s="4"/>
       <c r="P29" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
+      </c>
+      <c r="T29" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB29" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
-    <row r="30" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
+      <c r="O30" s="4"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>106</v>
+        <v>86</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB30" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
-    <row r="31" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
+      <c r="O31" s="4"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
+      </c>
+      <c r="T31" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X31" s="3">
         <v>12</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z31" s="3">
         <v>4</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB31" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC31" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD31" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="N32" s="3"/>
-      <c r="O32" s="3" t="s">
-        <v>50</v>
+      <c r="O32" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T32" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="V32" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB32" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
+      <c r="O33" s="4"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
+      </c>
+      <c r="T33" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X33" s="3">
         <v>12</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z33" s="3">
         <v>4</v>
       </c>
       <c r="AA33" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB33" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC33" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD33" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE33" s="3"/>
       <c r="AF33" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
+      <c r="O34" s="4"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="T34" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="X34" s="3">
         <v>12</v>
       </c>
       <c r="Y34" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="Z34" s="3">
         <v>4</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB34" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC34" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AD34" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
+      <c r="O35" s="4"/>
       <c r="P35" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="R35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T35" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U35" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="V35" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB35" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
+      <c r="O36" s="4"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>127</v>
+        <v>105</v>
+      </c>
+      <c r="T36" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AB36" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
     </row>
-    <row r="37" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
+      <c r="O37" s="4"/>
       <c r="P37" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="T37" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
+      </c>
+      <c r="T37" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB37" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="T38" s="3" t="s">
-        <v>141</v>
+        <v>115</v>
+      </c>
+      <c r="T38" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AB38" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
     </row>
-    <row r="39" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
+      <c r="O39" s="4"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>145</v>
+        <v>122</v>
+      </c>
+      <c r="T39" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB39" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
     </row>
-    <row r="40" spans="1:32" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>154</v>
+        <v>72</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
+      <c r="O40" s="4"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>148</v>
+        <v>128</v>
+      </c>
+      <c r="T40" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB40" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
@@ -5013,377 +5003,61 @@
       <c r="AF40" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF1" xr:uid="{3B918A07-AF31-4E8A-BA7B-30C90C452F60}"/>
+  <autoFilter ref="A1:AF40" xr:uid="{3B918A07-AF31-4E8A-BA7B-30C90C452F60}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="L2" r:id="rId1" xr:uid="{19A50234-077B-48E4-A86C-9A419CC7B586}"/>
     <hyperlink ref="L3" r:id="rId2" xr:uid="{48121C51-CCE3-481A-90AA-8865DCFCFB17}"/>
     <hyperlink ref="J5" r:id="rId3" xr:uid="{9689CCC1-6021-4E89-8C59-6E8FAA75F04A}"/>
-    <hyperlink ref="J6" r:id="rId4" xr:uid="{599E8438-CFE4-4055-B77D-1A2969EA40B5}"/>
-    <hyperlink ref="L6" r:id="rId5" xr:uid="{1A4B8E91-4607-42F3-B09A-53FCB71B99DC}"/>
-    <hyperlink ref="J7" r:id="rId6" xr:uid="{F52A0020-F1C1-4436-A601-B7229A4B3B53}"/>
-    <hyperlink ref="J8" r:id="rId7" xr:uid="{593E8B49-7638-4203-8F61-CDB7F05278F3}"/>
-    <hyperlink ref="J9" r:id="rId8" xr:uid="{2594DBFE-4787-4790-A171-B01DFCF5C52F}"/>
-    <hyperlink ref="L9" r:id="rId9" xr:uid="{49A96D2B-7C60-41FD-BF10-9E5297FB355C}"/>
-    <hyperlink ref="J11" r:id="rId10" xr:uid="{DD2924C5-2AE1-4887-A654-78B52C5F36D3}"/>
-    <hyperlink ref="L11" r:id="rId11" xr:uid="{0D7546BC-37DE-4227-8ED9-1AE9773DDBF5}"/>
-    <hyperlink ref="J12" r:id="rId12" xr:uid="{5537C1F5-3D2C-41E6-9A90-F13AA4AE267C}"/>
-    <hyperlink ref="L12" r:id="rId13" xr:uid="{CA847885-D84A-4893-B403-A275FC0109EB}"/>
-    <hyperlink ref="J13" r:id="rId14" xr:uid="{165C4032-666B-4B5E-8329-E87CA7BE8549}"/>
-    <hyperlink ref="J14" r:id="rId15" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C83308" xr:uid="{421BA401-5CD3-4974-8BB3-EF18A76670F5}"/>
-    <hyperlink ref="B2" r:id="rId16" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C106568" xr:uid="{2EEF0FE5-8279-4B2D-A590-2AFCDB31CB7B}"/>
-    <hyperlink ref="B3:B14" r:id="rId17" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C106568" xr:uid="{26A9DAF8-93CB-4680-9C6B-3A541399DF08}"/>
-    <hyperlink ref="L15" r:id="rId18" xr:uid="{E6A2058E-3B3C-40AA-8404-E356AC9C978F}"/>
-    <hyperlink ref="L16" r:id="rId19" xr:uid="{1C1F6B5B-124C-4FD5-AF36-55112A84DA4F}"/>
-    <hyperlink ref="J18" r:id="rId20" xr:uid="{56FD13CC-53FF-49B9-9B81-0B7F399F51E4}"/>
-    <hyperlink ref="J19" r:id="rId21" xr:uid="{8921FF44-6075-4CC4-B14E-C562CF45CF15}"/>
-    <hyperlink ref="L19" r:id="rId22" xr:uid="{68DA17FC-3934-442F-A1E1-85B738E8EDD0}"/>
-    <hyperlink ref="J20" r:id="rId23" xr:uid="{71AD83B1-C7BF-4EDD-AEBC-D2E1609E3942}"/>
-    <hyperlink ref="J21" r:id="rId24" xr:uid="{C997AE6F-AAC9-4A04-B7D2-829CA19B118C}"/>
-    <hyperlink ref="J22" r:id="rId25" xr:uid="{3CC4A7DA-A581-447B-BFD5-C81B704D7D62}"/>
-    <hyperlink ref="L22" r:id="rId26" xr:uid="{0A5D0AFB-F2F5-4829-BABF-2061039D0B14}"/>
-    <hyperlink ref="J24" r:id="rId27" xr:uid="{4DDF64F0-54CF-4C18-9950-2918566A1BD2}"/>
-    <hyperlink ref="L24" r:id="rId28" xr:uid="{EC4B3ADE-D34D-42A0-8C70-6307D16EC681}"/>
-    <hyperlink ref="J25" r:id="rId29" xr:uid="{45A5B3AB-43E9-4835-84EB-CCB17AC65CA5}"/>
-    <hyperlink ref="L25" r:id="rId30" xr:uid="{1349C1D3-4595-4536-937A-911A5DE84413}"/>
-    <hyperlink ref="J26" r:id="rId31" xr:uid="{1C4BE79F-CF84-4E15-B395-155A7A73B74C}"/>
-    <hyperlink ref="J27" r:id="rId32" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C83308" xr:uid="{D1579690-1320-4D95-893E-16DFA9AACADB}"/>
-    <hyperlink ref="B15" r:id="rId33" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C150823" xr:uid="{DD9B7DAC-D276-461D-A5E9-8565414D7765}"/>
-    <hyperlink ref="B16:B27" r:id="rId34" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C150823" xr:uid="{1290FA5C-21B0-49D6-8648-DC11C1E8CCEA}"/>
-    <hyperlink ref="L28" r:id="rId35" xr:uid="{729AA660-055C-4561-9AB3-ABCEEAEF4BC2}"/>
-    <hyperlink ref="L29" r:id="rId36" xr:uid="{0070FCA0-2027-4423-89AF-4CDB3410544F}"/>
-    <hyperlink ref="J31" r:id="rId37" xr:uid="{88876CCB-578E-41F1-96E1-8B851153740A}"/>
-    <hyperlink ref="J32" r:id="rId38" xr:uid="{8238E78C-65B2-489C-8EB8-F4D9BF14DBE9}"/>
-    <hyperlink ref="L32" r:id="rId39" xr:uid="{0C713CEE-FBE8-4207-86E2-9A8622BA88DF}"/>
-    <hyperlink ref="J33" r:id="rId40" xr:uid="{B16703F4-3874-42AA-B44B-D05BB8617A6E}"/>
-    <hyperlink ref="J34" r:id="rId41" xr:uid="{8B2814F7-853D-4676-AFF1-C7B125B4D60A}"/>
-    <hyperlink ref="J35" r:id="rId42" xr:uid="{BDCA12C8-5858-42C7-B543-A490BDA1305D}"/>
-    <hyperlink ref="L35" r:id="rId43" xr:uid="{AA7F752C-B675-4222-9C35-3E1052BBC1B3}"/>
-    <hyperlink ref="J37" r:id="rId44" xr:uid="{34E0E57B-B7A7-4A50-BB40-159F8DF20895}"/>
-    <hyperlink ref="L37" r:id="rId45" xr:uid="{83CEFF0B-073F-4EBA-9839-5E1D86618BF9}"/>
-    <hyperlink ref="J38" r:id="rId46" xr:uid="{EB510C28-76D9-4A30-A049-1A78B020D09E}"/>
-    <hyperlink ref="L38" r:id="rId47" xr:uid="{A11E8DED-DFB1-4A71-B839-5CDD4A70337B}"/>
-    <hyperlink ref="J39" r:id="rId48" xr:uid="{716222D4-514A-43BF-82BF-E4612FF0F641}"/>
-    <hyperlink ref="J40" r:id="rId49" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C83308" xr:uid="{A0D40F42-785A-44A0-81CF-BF8EA7F9DB77}"/>
-    <hyperlink ref="B28" r:id="rId50" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C25747" xr:uid="{09E891CE-3B5B-4D86-917C-94B210D7AE92}"/>
-    <hyperlink ref="B29:B40" r:id="rId51" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C25747" xr:uid="{9A749B80-800B-4B88-A8E2-1A363663D13E}"/>
+    <hyperlink ref="L6" r:id="rId4" xr:uid="{1A4B8E91-4607-42F3-B09A-53FCB71B99DC}"/>
+    <hyperlink ref="J7" r:id="rId5" xr:uid="{F52A0020-F1C1-4436-A601-B7229A4B3B53}"/>
+    <hyperlink ref="J8" r:id="rId6" xr:uid="{593E8B49-7638-4203-8F61-CDB7F05278F3}"/>
+    <hyperlink ref="L9" r:id="rId7" xr:uid="{49A96D2B-7C60-41FD-BF10-9E5297FB355C}"/>
+    <hyperlink ref="J11" r:id="rId8" xr:uid="{DD2924C5-2AE1-4887-A654-78B52C5F36D3}"/>
+    <hyperlink ref="L11" r:id="rId9" xr:uid="{0D7546BC-37DE-4227-8ED9-1AE9773DDBF5}"/>
+    <hyperlink ref="J12" r:id="rId10" xr:uid="{5537C1F5-3D2C-41E6-9A90-F13AA4AE267C}"/>
+    <hyperlink ref="L12" r:id="rId11" xr:uid="{CA847885-D84A-4893-B403-A275FC0109EB}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{165C4032-666B-4B5E-8329-E87CA7BE8549}"/>
+    <hyperlink ref="J14" r:id="rId13" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C83308" xr:uid="{421BA401-5CD3-4974-8BB3-EF18A76670F5}"/>
+    <hyperlink ref="B2" r:id="rId14" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C106568" xr:uid="{2EEF0FE5-8279-4B2D-A590-2AFCDB31CB7B}"/>
+    <hyperlink ref="B3:B14" r:id="rId15" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C106568" xr:uid="{26A9DAF8-93CB-4680-9C6B-3A541399DF08}"/>
+    <hyperlink ref="L15" r:id="rId16" xr:uid="{E6A2058E-3B3C-40AA-8404-E356AC9C978F}"/>
+    <hyperlink ref="L16" r:id="rId17" xr:uid="{1C1F6B5B-124C-4FD5-AF36-55112A84DA4F}"/>
+    <hyperlink ref="J18" r:id="rId18" xr:uid="{56FD13CC-53FF-49B9-9B81-0B7F399F51E4}"/>
+    <hyperlink ref="L19" r:id="rId19" xr:uid="{68DA17FC-3934-442F-A1E1-85B738E8EDD0}"/>
+    <hyperlink ref="J20" r:id="rId20" xr:uid="{71AD83B1-C7BF-4EDD-AEBC-D2E1609E3942}"/>
+    <hyperlink ref="J21" r:id="rId21" xr:uid="{C997AE6F-AAC9-4A04-B7D2-829CA19B118C}"/>
+    <hyperlink ref="L22" r:id="rId22" xr:uid="{0A5D0AFB-F2F5-4829-BABF-2061039D0B14}"/>
+    <hyperlink ref="J24" r:id="rId23" xr:uid="{4DDF64F0-54CF-4C18-9950-2918566A1BD2}"/>
+    <hyperlink ref="L24" r:id="rId24" xr:uid="{EC4B3ADE-D34D-42A0-8C70-6307D16EC681}"/>
+    <hyperlink ref="J25" r:id="rId25" xr:uid="{45A5B3AB-43E9-4835-84EB-CCB17AC65CA5}"/>
+    <hyperlink ref="L25" r:id="rId26" xr:uid="{1349C1D3-4595-4536-937A-911A5DE84413}"/>
+    <hyperlink ref="J26" r:id="rId27" xr:uid="{1C4BE79F-CF84-4E15-B395-155A7A73B74C}"/>
+    <hyperlink ref="J27" r:id="rId28" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C83308" xr:uid="{D1579690-1320-4D95-893E-16DFA9AACADB}"/>
+    <hyperlink ref="B15" r:id="rId29" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C150823" xr:uid="{DD9B7DAC-D276-461D-A5E9-8565414D7765}"/>
+    <hyperlink ref="B16:B27" r:id="rId30" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C150823" xr:uid="{1290FA5C-21B0-49D6-8648-DC11C1E8CCEA}"/>
+    <hyperlink ref="L28" r:id="rId31" xr:uid="{729AA660-055C-4561-9AB3-ABCEEAEF4BC2}"/>
+    <hyperlink ref="L29" r:id="rId32" xr:uid="{0070FCA0-2027-4423-89AF-4CDB3410544F}"/>
+    <hyperlink ref="J31" r:id="rId33" xr:uid="{88876CCB-578E-41F1-96E1-8B851153740A}"/>
+    <hyperlink ref="L32" r:id="rId34" xr:uid="{0C713CEE-FBE8-4207-86E2-9A8622BA88DF}"/>
+    <hyperlink ref="J33" r:id="rId35" xr:uid="{B16703F4-3874-42AA-B44B-D05BB8617A6E}"/>
+    <hyperlink ref="J34" r:id="rId36" xr:uid="{8B2814F7-853D-4676-AFF1-C7B125B4D60A}"/>
+    <hyperlink ref="L35" r:id="rId37" xr:uid="{AA7F752C-B675-4222-9C35-3E1052BBC1B3}"/>
+    <hyperlink ref="J37" r:id="rId38" xr:uid="{34E0E57B-B7A7-4A50-BB40-159F8DF20895}"/>
+    <hyperlink ref="L37" r:id="rId39" xr:uid="{83CEFF0B-073F-4EBA-9839-5E1D86618BF9}"/>
+    <hyperlink ref="J38" r:id="rId40" xr:uid="{EB510C28-76D9-4A30-A049-1A78B020D09E}"/>
+    <hyperlink ref="L38" r:id="rId41" xr:uid="{A11E8DED-DFB1-4A71-B839-5CDD4A70337B}"/>
+    <hyperlink ref="J39" r:id="rId42" xr:uid="{716222D4-514A-43BF-82BF-E4612FF0F641}"/>
+    <hyperlink ref="J40" r:id="rId43" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C83308" xr:uid="{A0D40F42-785A-44A0-81CF-BF8EA7F9DB77}"/>
+    <hyperlink ref="B28" r:id="rId44" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C25747" xr:uid="{09E891CE-3B5B-4D86-917C-94B210D7AE92}"/>
+    <hyperlink ref="B29:B40" r:id="rId45" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C25747" xr:uid="{9A749B80-800B-4B88-A8E2-1A363663D13E}"/>
+    <hyperlink ref="J6" r:id="rId46" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{CE248E48-8DCB-4EE4-9443-C32114FFD2BE}"/>
+    <hyperlink ref="J9" r:id="rId47" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{0CFB0400-146B-4ADA-A130-B7A6F8776888}"/>
+    <hyperlink ref="J19" r:id="rId48" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{0EB89630-A8DF-4DF9-8A6F-CCFF6B0925E1}"/>
+    <hyperlink ref="J22" r:id="rId49" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{0024C884-8369-4001-8674-1895F9A5B17B}"/>
+    <hyperlink ref="J32" r:id="rId50" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{BCEC3758-EA56-43DE-A437-5283117FF2F3}"/>
+    <hyperlink ref="J35" r:id="rId51" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{C173EC6B-4AC2-43F3-8BEA-2651FD5637F5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Description0 xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data.</Description0>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA3DD6FD0640724CAC6A104AA4040E53" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="866aaee467307fab2f51bbdbaaea79d8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dc215b4-4765-4137-95ef-e24fb8216673" xmlns:ns3="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636a025d234e12dfc0e20f1263040641" ns2:_="" ns3:_="">
-    <xsd:import namespace="3dc215b4-4765-4137-95ef-e24fb8216673"/>
-    <xsd:import namespace="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:Description0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3dc215b4-4765-4137-95ef-e24fb8216673" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Description0" ma:index="10" ma:displayName="Description" ma:default="Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data." ma:description="Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data." ma:format="Dropdown" ma:internalName="Description0">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="11" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="15" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="18" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="19" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4c04c6af-d60c-4670-8c9c-7f80a3ec6f31" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="13" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="14" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{38ff5dc4-14b9-4dbb-b87c-ec2ec2bd61dd}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5272086F-62E2-4B40-8A1B-27A23F471E44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
-    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18759BAB-932F-4F7D-873C-75BCE76A7311}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1416443D-A0DD-4001-85AA-A994B5EAD11C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
-    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/curation/draft/package16/R16_BC_LB_New.xlsx
+++ b/curation/draft/package16/R16_BC_LB_New.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F602DD5-331F-436E-9F42-83CDDEE25E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB3252A-F44E-44D8-88FD-51A26796B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F590C486-C613-40E0-BF06-47BB8CB37E44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F590C486-C613-40E0-BF06-47BB8CB37E44}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_LB_Edits" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="193">
   <si>
     <t>package_date</t>
   </si>
@@ -447,9 +447,6 @@
     <t>Laboratory Tests;Chemistry Tests;Clearance Rates</t>
   </si>
   <si>
-    <t>Sodium Clearance in Urine</t>
-  </si>
-  <si>
     <t>C49237</t>
   </si>
   <si>
@@ -498,26 +495,137 @@
     <t>Laboratory Tests;Chemistry Tests;Clearance Rates;Creatinine Measurements</t>
   </si>
   <si>
-    <t>Creatinine Clearance in Urine</t>
-  </si>
-  <si>
     <t>Creatinine Clearance</t>
   </si>
   <si>
-    <t>NACLRURIN</t>
-  </si>
-  <si>
-    <t>CREATCLRRURIN</t>
+    <t>C74761</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine;Albumin/creatinine ratio;Albumin/creatinine ratio measurement;Microalbumin/Creatinine Ratio;ALBCREAT</t>
+  </si>
+  <si>
+    <t>g/kg;mmol/mol;g/mol</t>
+  </si>
+  <si>
+    <t>Urine</t>
+  </si>
+  <si>
+    <t>C103453</t>
+  </si>
+  <si>
+    <t>The determination of the ratio of albumin compared to creatinine present in a sample. The measurement may be expressed as a ratio or percentage.</t>
+  </si>
+  <si>
+    <t>C64431</t>
+  </si>
+  <si>
+    <t>The determination of the ratio of the albumin compared with total protein in a biological sample. The measurement may be expressed as a ratio or percentage.</t>
+  </si>
+  <si>
+    <t>C105706</t>
+  </si>
+  <si>
+    <t>SERUM OR PLASMA</t>
+  </si>
+  <si>
+    <t>Sodium Clearance in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>Creatinine Clearance in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>Laboratory Tests;Chemistry Tests; Ratio Measurements</t>
+  </si>
+  <si>
+    <t>Laboratory Tests;Chemistry Tests;Ratio Measurements</t>
+  </si>
+  <si>
+    <t>Albumin/Total Protein;ALBPROT</t>
+  </si>
+  <si>
+    <t>ALBCREATURIN</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine in Urine</t>
+  </si>
+  <si>
+    <t>ALBCREAT</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine</t>
+  </si>
+  <si>
+    <t>C73721</t>
+  </si>
+  <si>
+    <t>g/mol</t>
+  </si>
+  <si>
+    <t>ALBPROTURIN</t>
+  </si>
+  <si>
+    <t>ALBPROT</t>
+  </si>
+  <si>
+    <t>Albumin/Total Protein</t>
+  </si>
+  <si>
+    <t>Albumin/Total Protein in Urine</t>
+  </si>
+  <si>
+    <t>13992-3</t>
+  </si>
+  <si>
+    <t>14959-1</t>
+  </si>
+  <si>
+    <t>Serum;Plasma;Urine</t>
+  </si>
+  <si>
+    <t>%;Ratio</t>
+  </si>
+  <si>
+    <t>C48566</t>
+  </si>
+  <si>
+    <t>Unit of Mass Fraction</t>
+  </si>
+  <si>
+    <t>C179809</t>
+  </si>
+  <si>
+    <t>Ratio Result Type</t>
+  </si>
+  <si>
+    <t>C70453</t>
+  </si>
+  <si>
+    <t>g/g</t>
+  </si>
+  <si>
+    <t>%;g/g;g/kg</t>
   </si>
   <si>
     <t>mmol/day;mmol/min;mmol/s</t>
+  </si>
+  <si>
+    <t>NACLRSERPL</t>
+  </si>
+  <si>
+    <t>CREATCLRSERPL</t>
+  </si>
+  <si>
+    <t>Albumin to Creatinine Ratio Measurement</t>
+  </si>
+  <si>
+    <t>Albumin to Total Protein Ratio Measurement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,6 +676,25 @@
       <sz val="9.5"/>
       <color rgb="FF112277"/>
       <name val="Albany AMT"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Albany AMT"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -638,7 +765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -664,6 +791,17 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1000,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C17BFEF-212D-4B25-A8DF-125FBA186BFE}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" customWidth="1"/>
@@ -1009,7 +1147,7 @@
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.7109375" style="7" customWidth="1"/>
     <col min="10" max="11" width="4" customWidth="1"/>
@@ -1146,7 +1284,7 @@
         <v>18</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -1390,7 +1528,7 @@
         <v>131</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>134</v>
@@ -1420,7 +1558,7 @@
         <v>18</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1437,7 +1575,7 @@
         <v>131</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>134</v>
@@ -1482,7 +1620,7 @@
         <v>131</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>134</v>
@@ -1527,7 +1665,7 @@
         <v>131</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>134</v>
@@ -1574,7 +1712,7 @@
         <v>131</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>134</v>
@@ -1619,7 +1757,7 @@
         <v>131</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>134</v>
@@ -1655,28 +1793,28 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="F15" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -1694,7 +1832,7 @@
         <v>18</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -1702,28 +1840,28 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>47</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1747,28 +1885,28 @@
         <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>47</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1792,28 +1930,28 @@
         <v>12</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>47</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1839,28 +1977,28 @@
         <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>47</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1884,28 +2022,28 @@
         <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>47</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -1923,6 +2061,464 @@
         <v>19</v>
       </c>
       <c r="Q20" s="4"/>
+    </row>
+    <row r="21" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q21" s="13"/>
+    </row>
+    <row r="22" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="13"/>
+    </row>
+    <row r="24" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q25" s="13"/>
+    </row>
+    <row r="26" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q26" s="13"/>
+    </row>
+    <row r="27" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="P27" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q28" s="13"/>
+    </row>
+    <row r="29" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q29" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q30" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1960,6 +2556,25 @@
     <hyperlink ref="D16:D20" r:id="rId31" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C25747" xr:uid="{A0535F2C-941A-4CB4-A26B-2C489D84AC33}"/>
     <hyperlink ref="E15" r:id="rId32" xr:uid="{78AF8481-5187-4894-A212-B328E28E5223}"/>
     <hyperlink ref="E16:E20" r:id="rId33" display="C64547" xr:uid="{78624BAF-4F40-404D-8BF6-2ED0702F114F}"/>
+    <hyperlink ref="D21" r:id="rId34" xr:uid="{B6D64340-156A-4DF2-9ED1-3F8D21D3EBDB}"/>
+    <hyperlink ref="N21" r:id="rId35" xr:uid="{7BC074A0-F546-4481-8FF3-DF1EEDDD9789}"/>
+    <hyperlink ref="D22" r:id="rId36" xr:uid="{A079D635-8C50-4CE0-ACFF-5C4DFEA7B494}"/>
+    <hyperlink ref="D23" r:id="rId37" xr:uid="{33194B68-E4EF-4BB7-851F-FD31C3C27B61}"/>
+    <hyperlink ref="N23" r:id="rId38" xr:uid="{649C65A7-F80F-460D-88DA-A21A263A66B3}"/>
+    <hyperlink ref="D24" r:id="rId39" xr:uid="{FED03F2E-9BB8-45C6-A897-F769FF74407E}"/>
+    <hyperlink ref="N24" r:id="rId40" xr:uid="{7254A956-4774-4F7D-B601-BBBC73BAE9B7}"/>
+    <hyperlink ref="D25" r:id="rId41" xr:uid="{CD1009FE-AF8A-4683-A562-A3F61012D6A9}"/>
+    <hyperlink ref="N25" r:id="rId42" xr:uid="{252D1249-B4BB-4D5A-93FD-E8C74220BEB5}"/>
+    <hyperlink ref="N26" r:id="rId43" xr:uid="{C7633519-C54E-4473-83CC-1BCA53EC9D37}"/>
+    <hyperlink ref="N28" r:id="rId44" xr:uid="{F8787EB5-ADCF-4E4B-B0BF-5E8AB923984D}"/>
+    <hyperlink ref="N29" r:id="rId45" xr:uid="{C53520D8-6C19-4BE3-82B8-1C861F440B63}"/>
+    <hyperlink ref="N30" r:id="rId46" xr:uid="{6A96F2C4-BB35-453E-B711-24B41A6DC0BD}"/>
+    <hyperlink ref="D26" r:id="rId47" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C103453" xr:uid="{3BE34F94-8EF3-4F54-AAF3-71F2A0F717D6}"/>
+    <hyperlink ref="D27:D30" r:id="rId48" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C103453" xr:uid="{8E382FC0-FBD3-45C9-BF78-C841D7C942DB}"/>
+    <hyperlink ref="E21" r:id="rId49" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C64431" xr:uid="{A9DE398D-52A7-4C3C-819A-5081393A1AFA}"/>
+    <hyperlink ref="E22:E30" r:id="rId50" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C64431" xr:uid="{BFDBF815-CB2C-4CDE-9693-261AB95F9A9B}"/>
+    <hyperlink ref="N27" r:id="rId51" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48566" xr:uid="{742F04F7-6BC9-425F-BB3C-FCD18863F07E}"/>
+    <hyperlink ref="N22" r:id="rId52" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C179809" xr:uid="{777A788C-EAA2-4333-ADCD-4F44BC1E0919}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1967,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B918A07-AF31-4E8A-BA7B-30C90C452F60}">
-  <dimension ref="A1:AF40"/>
+  <dimension ref="A1:AF64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1976,6 +2591,7 @@
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
     <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.42578125" customWidth="1"/>
     <col min="17" max="17" width="29.7109375" customWidth="1"/>
@@ -2082,979 +2698,979 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="G2" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="J2" s="11"/>
+      <c r="K2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="3" t="s">
+      <c r="N2" s="11"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF2" s="11"/>
+    </row>
+    <row r="3" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q3" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="R2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" s="3" t="s">
+      <c r="R3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="T2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3" t="s">
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+    </row>
+    <row r="4" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11"/>
+    </row>
+    <row r="5" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X5" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z5" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N6" s="11"/>
+      <c r="O6" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="T7" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X7" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y7" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z7" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE7" s="11"/>
+      <c r="AF7" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="T8" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X8" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y8" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z8" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE8" s="11"/>
+      <c r="AF8" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="11"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB9" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC9" s="11"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="T10" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC10" s="11"/>
+      <c r="AD10" s="11"/>
+      <c r="AE10" s="11"/>
+      <c r="AF10" s="11"/>
+    </row>
+    <row r="11" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N11" s="11"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="R11" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="T11" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AF2" s="3"/>
-    </row>
-    <row r="3" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="AF11" s="11"/>
+    </row>
+    <row r="12" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F12" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="3" t="s">
+      <c r="G12" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="T12" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC12" s="11"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
+      <c r="AF12" s="11"/>
+    </row>
+    <row r="13" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="V3" s="3" t="s">
+      <c r="C13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="T13" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V13" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-    </row>
-    <row r="4" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
+    </row>
+    <row r="14" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="V4" s="3" t="s">
+      <c r="G14" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T14" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V14" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-    </row>
-    <row r="5" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X5" s="3">
-        <v>12</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD5" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X7" s="3">
-        <v>12</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X8" s="3">
-        <v>12</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-    </row>
-    <row r="11" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T12" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-    </row>
-    <row r="13" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-    </row>
-    <row r="14" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="T14" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC14" s="11"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="11"/>
+      <c r="AF14" s="11"/>
     </row>
     <row r="15" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -3074,10 +3690,10 @@
         <v>72</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>73</v>
@@ -3150,10 +3766,10 @@
         <v>72</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>79</v>
@@ -3224,10 +3840,10 @@
         <v>72</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>86</v>
@@ -3290,10 +3906,10 @@
         <v>72</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>90</v>
@@ -3372,10 +3988,10 @@
         <v>72</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>97</v>
@@ -3394,7 +4010,7 @@
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -3448,10 +4064,10 @@
         <v>72</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>102</v>
@@ -3530,10 +4146,10 @@
         <v>72</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>103</v>
@@ -3612,10 +4228,10 @@
         <v>72</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>104</v>
@@ -3635,10 +4251,10 @@
       <c r="N22" s="3"/>
       <c r="O22" s="4"/>
       <c r="P22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>83</v>
@@ -3690,10 +4306,10 @@
         <v>72</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>105</v>
@@ -3756,10 +4372,10 @@
         <v>72</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>108</v>
@@ -3834,10 +4450,10 @@
         <v>72</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>115</v>
@@ -3910,10 +4526,10 @@
         <v>72</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>122</v>
@@ -3978,10 +4594,10 @@
         <v>72</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>128</v>
@@ -4028,979 +4644,2794 @@
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
-    <row r="28" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" s="3" t="s">
+    <row r="28" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3" t="s">
+      <c r="D28" s="11"/>
+      <c r="E28" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="G28" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="N28" s="11"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q28" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="R28" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="S28" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="T28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="V28" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="W28" s="11"/>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
+      <c r="Z28" s="11"/>
+      <c r="AA28" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC28" s="11"/>
+      <c r="AD28" s="11"/>
+      <c r="AE28" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF28" s="11"/>
+    </row>
+    <row r="29" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N29" s="11"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q29" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R29" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S29" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="T29" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="V29" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="11"/>
+      <c r="AA29" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB29" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC29" s="11"/>
+      <c r="AD29" s="11"/>
+      <c r="AE29" s="11"/>
+      <c r="AF29" s="11"/>
+    </row>
+    <row r="30" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R30" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S30" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="U30" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="V30" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11"/>
+      <c r="AA30" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB30" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC30" s="11"/>
+      <c r="AD30" s="11"/>
+      <c r="AE30" s="11"/>
+      <c r="AF30" s="11"/>
+    </row>
+    <row r="31" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S31" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="T31" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U31" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V31" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W31" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X31" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y31" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z31" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA31" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB31" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC31" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD31" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE31" s="11"/>
+      <c r="AF31" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N32" s="11"/>
+      <c r="O32" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S32" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T32" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="U32" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V32" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB32" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC32" s="11"/>
+      <c r="AD32" s="11"/>
+      <c r="AE32" s="11"/>
+      <c r="AF32" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="T33" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U33" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V33" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W33" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X33" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y33" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z33" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA33" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC33" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD33" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE33" s="11"/>
+      <c r="AF33" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S34" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="T34" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U34" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V34" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W34" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X34" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y34" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z34" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA34" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB34" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC34" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD34" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE34" s="11"/>
+      <c r="AF34" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N35" s="11"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q35" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="R35" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S35" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="T35" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="U35" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V35" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+      <c r="Y35" s="11"/>
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC35" s="11"/>
+      <c r="AD35" s="11"/>
+      <c r="AE35" s="11"/>
+      <c r="AF35" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S36" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="T36" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="U36" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="V36" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W36" s="11"/>
+      <c r="X36" s="11"/>
+      <c r="Y36" s="11"/>
+      <c r="Z36" s="11"/>
+      <c r="AA36" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB36" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC36" s="11"/>
+      <c r="AD36" s="11"/>
+      <c r="AE36" s="11"/>
+      <c r="AF36" s="11"/>
+    </row>
+    <row r="37" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N37" s="11"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q37" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="R37" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S37" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="T37" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="U37" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="V37" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
+      <c r="Y37" s="11"/>
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB37" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC37" s="11"/>
+      <c r="AD37" s="11"/>
+      <c r="AE37" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF37" s="11"/>
+    </row>
+    <row r="38" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="N38" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S38" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="T38" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="U38" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="V38" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB38" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC38" s="11"/>
+      <c r="AD38" s="11"/>
+      <c r="AE38" s="11"/>
+      <c r="AF38" s="11"/>
+    </row>
+    <row r="39" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="S39" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="T39" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="U39" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V39" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W39" s="11"/>
+      <c r="X39" s="11"/>
+      <c r="Y39" s="11"/>
+      <c r="Z39" s="11"/>
+      <c r="AA39" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB39" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC39" s="11"/>
+      <c r="AD39" s="11"/>
+      <c r="AE39" s="11"/>
+      <c r="AF39" s="11"/>
+    </row>
+    <row r="40" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="S40" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T40" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="U40" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V40" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W40" s="11"/>
+      <c r="X40" s="11"/>
+      <c r="Y40" s="11"/>
+      <c r="Z40" s="11"/>
+      <c r="AA40" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB40" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC40" s="11"/>
+      <c r="AD40" s="11"/>
+      <c r="AE40" s="11"/>
+      <c r="AF40" s="11"/>
+    </row>
+    <row r="41" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="N41" s="11"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q41" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="R41" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="S41" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="T41" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="U41" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="V41" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="11"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB41" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC41" s="11"/>
+      <c r="AD41" s="11"/>
+      <c r="AE41" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF41" s="11"/>
+    </row>
+    <row r="42" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N42" s="11"/>
+      <c r="O42" s="13"/>
+      <c r="P42" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q42" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="R42" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S42" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="T42" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="U42" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="V42" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W42" s="11"/>
+      <c r="X42" s="11"/>
+      <c r="Y42" s="11"/>
+      <c r="Z42" s="11"/>
+      <c r="AA42" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB42" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC42" s="11"/>
+      <c r="AD42" s="11"/>
+      <c r="AE42" s="11"/>
+      <c r="AF42" s="11"/>
+    </row>
+    <row r="43" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R43" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S43" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T43" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="V43" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W43" s="11"/>
+      <c r="X43" s="11"/>
+      <c r="Y43" s="11"/>
+      <c r="Z43" s="11"/>
+      <c r="AA43" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB43" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC43" s="11"/>
+      <c r="AD43" s="11"/>
+      <c r="AE43" s="11"/>
+      <c r="AF43" s="11"/>
+    </row>
+    <row r="44" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S44" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="T44" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U44" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V44" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W44" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X44" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y44" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z44" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA44" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB44" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC44" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD44" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE44" s="11"/>
+      <c r="AF44" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="O45" s="13"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="R45" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S45" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T45" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="U45" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V45" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="11"/>
+      <c r="AA45" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB45" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC45" s="11"/>
+      <c r="AD45" s="11"/>
+      <c r="AE45" s="11"/>
+      <c r="AF45" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S46" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="T46" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U46" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V46" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W46" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X46" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y46" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z46" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA46" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB46" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC46" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD46" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE46" s="11"/>
+      <c r="AF46" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="T47" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U47" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V47" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W47" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X47" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y47" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z47" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA47" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB47" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC47" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD47" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE47" s="11"/>
+      <c r="AF47" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L48" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N48" s="11"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q48" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="R48" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S48" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="T48" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="U48" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="V48" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="W48" s="11"/>
+      <c r="X48" s="11"/>
+      <c r="Y48" s="11"/>
+      <c r="Z48" s="11"/>
+      <c r="AA48" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB48" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC48" s="11"/>
+      <c r="AD48" s="11"/>
+      <c r="AE48" s="11"/>
+      <c r="AF48" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="R49" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S49" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="T49" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="U49" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="V49" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W49" s="11"/>
+      <c r="X49" s="11"/>
+      <c r="Y49" s="11"/>
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB49" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC49" s="11"/>
+      <c r="AD49" s="11"/>
+      <c r="AE49" s="11"/>
+      <c r="AF49" s="11"/>
+    </row>
+    <row r="50" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N50" s="11"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q50" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="R50" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S50" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="T50" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="U50" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="V50" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+      <c r="Y50" s="11"/>
+      <c r="Z50" s="11"/>
+      <c r="AA50" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB50" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC50" s="11"/>
+      <c r="AD50" s="11"/>
+      <c r="AE50" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF50" s="11"/>
+    </row>
+    <row r="51" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L51" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="O51" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="11"/>
+      <c r="R51" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S51" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="T51" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="U51" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="V51" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W51" s="11"/>
+      <c r="X51" s="11"/>
+      <c r="Y51" s="11"/>
+      <c r="Z51" s="11"/>
+      <c r="AA51" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB51" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC51" s="11"/>
+      <c r="AD51" s="11"/>
+      <c r="AE51" s="11"/>
+      <c r="AF51" s="11"/>
+    </row>
+    <row r="52" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="S52" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="T52" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="U52" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V52" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="W52" s="11"/>
+      <c r="X52" s="11"/>
+      <c r="Y52" s="11"/>
+      <c r="Z52" s="11"/>
+      <c r="AA52" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB52" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC52" s="11"/>
+      <c r="AD52" s="11"/>
+      <c r="AE52" s="11"/>
+      <c r="AF52" s="11"/>
+    </row>
+    <row r="53" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="C53" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L28" s="6" t="s">
+      <c r="J53" s="3"/>
+      <c r="K53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L53" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="M53" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="R28" s="3" t="s">
+      <c r="N53" s="3"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="R53" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="S28" s="3" t="s">
+      <c r="S53" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="T28" s="4" t="s">
+      <c r="T53" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="U28" s="3" t="s">
+      <c r="U53" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="V28" s="3" t="s">
+      <c r="V53" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB28" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3" t="s">
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC53" s="3"/>
+      <c r="AD53" s="3"/>
+      <c r="AE53" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AF28" s="3"/>
-    </row>
-    <row r="29" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="AF53" s="3"/>
+    </row>
+    <row r="54" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3" t="s">
+      <c r="D54" s="3"/>
+      <c r="E54" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F54" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H29" s="4" t="s">
+      <c r="G54" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N54" s="3"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="Q54" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="T54" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC54" s="3"/>
+      <c r="AD54" s="3"/>
+      <c r="AE54" s="3"/>
+      <c r="AF54" s="3"/>
+    </row>
+    <row r="55" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R55" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="T29" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="S55" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T55" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U55" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="V55" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC29" s="3"/>
-      <c r="AD29" s="3"/>
-      <c r="AE29" s="3"/>
-      <c r="AF29" s="3"/>
-    </row>
-    <row r="30" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB55" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3" t="s">
+      <c r="D56" s="3"/>
+      <c r="E56" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F56" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" s="4" t="s">
+      <c r="G56" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T56" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="U56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V56" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W56" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X56" s="3">
+        <v>12</v>
+      </c>
+      <c r="Y56" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z56" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB56" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC56" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD56" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="R30" s="3" t="s">
+      <c r="C57" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N57" s="3"/>
+      <c r="O57" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="S30" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="T30" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="V30" s="3" t="s">
+      <c r="S57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T57" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="T58" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V58" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB30" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC30" s="3"/>
-      <c r="AD30" s="3"/>
-      <c r="AE30" s="3"/>
-      <c r="AF30" s="3"/>
-    </row>
-    <row r="31" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="W58" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X58" s="3">
+        <v>12</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3" t="s">
+      <c r="D59" s="3"/>
+      <c r="E59" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H31" s="4" t="s">
+      <c r="G59" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T59" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X59" s="3">
+        <v>12</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3" t="s">
+      <c r="C60" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N60" s="3"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="R60" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="S31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="T31" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="V31" s="3" t="s">
+      <c r="S60" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T60" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+      <c r="AE60" s="3"/>
+      <c r="AF60" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T61" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="U61" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="V61" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="W31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X31" s="3">
-        <v>12</v>
-      </c>
-      <c r="Y31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z31" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA31" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC31" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB61" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+    </row>
+    <row r="62" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3" t="s">
+      <c r="D62" s="3"/>
+      <c r="E62" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H32" s="4" t="s">
+      <c r="G62" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="N62" s="3"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="T62" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC62" s="3"/>
+      <c r="AD62" s="3"/>
+      <c r="AE62" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF62" s="3"/>
+    </row>
+    <row r="63" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3" t="s">
+      <c r="C63" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T32" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC32" s="3"/>
-      <c r="AD32" s="3"/>
-      <c r="AE32" s="3"/>
-      <c r="AF32" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="S63" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="T63" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="U63" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="V63" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB63" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3"/>
+      <c r="AF63" s="3"/>
+    </row>
+    <row r="64" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3" t="s">
+      <c r="D64" s="3"/>
+      <c r="E64" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F64" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="T33" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="V33" s="3" t="s">
+      <c r="G64" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="T64" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="U64" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="V64" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X33" s="3">
-        <v>12</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC33" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T34" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="V34" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X34" s="3">
-        <v>12</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z34" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA34" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC34" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE34" s="3"/>
-      <c r="AF34" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N35" s="3"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T35" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB35" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC35" s="3"/>
-      <c r="AD35" s="3"/>
-      <c r="AE35" s="3"/>
-      <c r="AF35" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="T36" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB36" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC36" s="3"/>
-      <c r="AD36" s="3"/>
-      <c r="AE36" s="3"/>
-      <c r="AF36" s="3"/>
-    </row>
-    <row r="37" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="N37" s="3"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="T37" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="V37" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB37" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC37" s="3"/>
-      <c r="AD37" s="3"/>
-      <c r="AE37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF37" s="3"/>
-    </row>
-    <row r="38" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O38" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T38" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="V38" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB38" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC38" s="3"/>
-      <c r="AD38" s="3"/>
-      <c r="AE38" s="3"/>
-      <c r="AF38" s="3"/>
-    </row>
-    <row r="39" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="T39" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="U39" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="V39" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC39" s="3"/>
-      <c r="AD39" s="3"/>
-      <c r="AE39" s="3"/>
-      <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="T40" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="V40" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB40" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC40" s="3"/>
-      <c r="AD40" s="3"/>
-      <c r="AE40" s="3"/>
-      <c r="AF40" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC64" s="3"/>
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3"/>
+      <c r="AF64" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AF40" xr:uid="{3B918A07-AF31-4E8A-BA7B-30C90C452F60}"/>
@@ -5057,6 +7488,47 @@
     <hyperlink ref="J22" r:id="rId49" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{0024C884-8369-4001-8674-1895F9A5B17B}"/>
     <hyperlink ref="J32" r:id="rId50" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{BCEC3758-EA56-43DE-A437-5283117FF2F3}"/>
     <hyperlink ref="J35" r:id="rId51" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48567" xr:uid="{C173EC6B-4AC2-43F3-8BEA-2651FD5637F5}"/>
+    <hyperlink ref="L41" r:id="rId52" xr:uid="{B5F42E7C-4EE1-4829-A9FF-331ED4C5E3D4}"/>
+    <hyperlink ref="L42" r:id="rId53" xr:uid="{1EE10C45-E47D-49F3-AB80-4403A59346EA}"/>
+    <hyperlink ref="J44" r:id="rId54" xr:uid="{9765451C-C1E8-4940-8585-665B7474A589}"/>
+    <hyperlink ref="L45" r:id="rId55" xr:uid="{8BD2764B-BAC1-48C8-92B9-6F12AA4AB8C9}"/>
+    <hyperlink ref="J46" r:id="rId56" xr:uid="{6238A7E4-D8A3-4C8F-B619-A33BC9B6A7EE}"/>
+    <hyperlink ref="J47" r:id="rId57" xr:uid="{6F333945-B3C7-4135-8D06-4571249AE61F}"/>
+    <hyperlink ref="L48" r:id="rId58" xr:uid="{B93927A2-3FD3-4FFA-BF22-EF999FED9CD3}"/>
+    <hyperlink ref="J50" r:id="rId59" xr:uid="{9DAA3907-B062-424F-95FC-6E3FAABCA555}"/>
+    <hyperlink ref="L50" r:id="rId60" xr:uid="{5D253358-092A-44A2-A0F5-79552DE08D74}"/>
+    <hyperlink ref="J51" r:id="rId61" xr:uid="{1BD1ED45-0244-44DF-A5EF-5E3D16958C9B}"/>
+    <hyperlink ref="L51" r:id="rId62" xr:uid="{30344E88-8116-483B-988E-782F5598F6ED}"/>
+    <hyperlink ref="J52" r:id="rId63" xr:uid="{5A27A48A-56DE-45CD-9B86-36AAF8DF2CCA}"/>
+    <hyperlink ref="B41:B52" r:id="rId64" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C103453" xr:uid="{3D739A99-34C2-488E-BE91-8A6CD1D53E18}"/>
+    <hyperlink ref="B53" r:id="rId65" xr:uid="{509BA2EB-9CC0-464A-8C04-4BB9B0497C62}"/>
+    <hyperlink ref="L53" r:id="rId66" xr:uid="{6E18949D-B6E4-4249-B82A-14D4FCDB639A}"/>
+    <hyperlink ref="B54" r:id="rId67" xr:uid="{3D38E41C-89D1-4DA1-BCE6-D475749F8F34}"/>
+    <hyperlink ref="L54" r:id="rId68" xr:uid="{8D2F452B-A8B0-40D3-91D0-2B6A362635F7}"/>
+    <hyperlink ref="B55" r:id="rId69" xr:uid="{17647B59-A5D1-48BF-9592-174B0B35009E}"/>
+    <hyperlink ref="B56" r:id="rId70" xr:uid="{BFB8D452-3C38-40A6-BAC0-F9BE709054CE}"/>
+    <hyperlink ref="J56" r:id="rId71" xr:uid="{B029202D-EB2E-4D8E-BFD8-141CAFD78CBC}"/>
+    <hyperlink ref="B57" r:id="rId72" xr:uid="{202BE89B-4435-48FA-B09E-CFCA30033911}"/>
+    <hyperlink ref="L57" r:id="rId73" xr:uid="{9BCDA306-C0ED-4D53-8DE9-F6683119D9AA}"/>
+    <hyperlink ref="B58" r:id="rId74" xr:uid="{395DE072-A6B3-4DA3-B0C5-A9A901011348}"/>
+    <hyperlink ref="J58" r:id="rId75" xr:uid="{A8681C9E-527F-4BD9-8AF4-A5C5F296AF93}"/>
+    <hyperlink ref="B59" r:id="rId76" xr:uid="{4A9C2828-BA7E-4727-9F95-799EAFC0CD66}"/>
+    <hyperlink ref="J59" r:id="rId77" xr:uid="{2104B682-BEA4-47E1-8CF9-77B3CE6D3F43}"/>
+    <hyperlink ref="B60" r:id="rId78" xr:uid="{10F0B3CB-F8EC-4EF9-B029-09967BE4310D}"/>
+    <hyperlink ref="L60" r:id="rId79" xr:uid="{1BEBEC5E-D18B-4D16-9B9E-87B19EA9EB91}"/>
+    <hyperlink ref="B61" r:id="rId80" xr:uid="{2038E853-27E9-4DEE-8568-4B3492C8A7D7}"/>
+    <hyperlink ref="B62" r:id="rId81" xr:uid="{60BDA780-DA49-4933-96C8-69A0D6EF322C}"/>
+    <hyperlink ref="J62" r:id="rId82" xr:uid="{F062050C-BF86-4D89-8192-F83D037FED8D}"/>
+    <hyperlink ref="L62" r:id="rId83" xr:uid="{04AB3B69-78C4-414F-8513-BD72BC5A83F6}"/>
+    <hyperlink ref="B63" r:id="rId84" xr:uid="{4764F3B6-B6B4-4513-84FA-0BAF1F8FC459}"/>
+    <hyperlink ref="J63" r:id="rId85" xr:uid="{C0E7C38D-B0A7-4C53-AB48-DA6E2CA2952D}"/>
+    <hyperlink ref="L63" r:id="rId86" xr:uid="{9E7F0A5F-1777-4C8A-A53F-2B6F3601FCC9}"/>
+    <hyperlink ref="B64" r:id="rId87" xr:uid="{A1A2BC31-6978-48A6-B219-307F7A5C6FFD}"/>
+    <hyperlink ref="J64" r:id="rId88" xr:uid="{773721F9-2D47-4521-A598-75DD2DAF20F5}"/>
+    <hyperlink ref="J57" r:id="rId89" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C179809" xr:uid="{1677C90C-2BC8-4F9A-B0BA-E91391A190AD}"/>
+    <hyperlink ref="J60" r:id="rId90" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C179809" xr:uid="{D8825E05-90E7-431F-AFE8-0E52D782B3EB}"/>
+    <hyperlink ref="J45" r:id="rId91" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48566" xr:uid="{85B63EFB-06C2-4577-9422-3CCCC23C1754}"/>
+    <hyperlink ref="J48" r:id="rId92" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C48566" xr:uid="{4EC6B1FD-433D-401B-AC25-FAAC0FE6FE55}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/curation/draft/package16/R16_BC_LB_New.xlsx
+++ b/curation/draft/package16/R16_BC_LB_New.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F77040-82F2-4869-9A3F-973F3AE94B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6C3C5C-D573-47F5-866B-1656CAA125BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F590C486-C613-40E0-BF06-47BB8CB37E44}"/>
   </bookViews>
@@ -3071,7 +3071,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B918A07-AF31-4E8A-BA7B-30C90C452F60}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AG192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3194,7 +3193,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>12</v>
       </c>
@@ -3270,7 +3269,7 @@
       </c>
       <c r="AF2" s="11"/>
     </row>
-    <row r="3" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
@@ -3344,7 +3343,7 @@
       <c r="AE3" s="11"/>
       <c r="AF3" s="11"/>
     </row>
-    <row r="4" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>12</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
@@ -3813,7 +3812,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>12</v>
       </c>
@@ -3879,7 +3878,7 @@
       <c r="AE10" s="11"/>
       <c r="AF10" s="11"/>
     </row>
-    <row r="11" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>12</v>
       </c>
@@ -3957,7 +3956,7 @@
       </c>
       <c r="AF11" s="11"/>
     </row>
-    <row r="12" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>12</v>
       </c>
@@ -4033,7 +4032,7 @@
       <c r="AE12" s="11"/>
       <c r="AF12" s="11"/>
     </row>
-    <row r="13" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>12</v>
       </c>
@@ -4101,7 +4100,7 @@
       <c r="AE13" s="11"/>
       <c r="AF13" s="11"/>
     </row>
-    <row r="14" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>12</v>
       </c>
@@ -4169,7 +4168,7 @@
       <c r="AE14" s="11"/>
       <c r="AF14" s="11"/>
     </row>
-    <row r="15" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
@@ -4245,7 +4244,7 @@
       </c>
       <c r="AF15" s="3"/>
     </row>
-    <row r="16" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
@@ -4319,7 +4318,7 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
     </row>
-    <row r="17" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4467,7 +4466,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>12</v>
       </c>
@@ -4707,7 +4706,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
@@ -4785,7 +4784,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>12</v>
       </c>
@@ -4851,7 +4850,7 @@
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
     </row>
-    <row r="24" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>12</v>
       </c>
@@ -4929,7 +4928,7 @@
       </c>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>12</v>
       </c>
@@ -5005,7 +5004,7 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>12</v>
       </c>
@@ -5073,7 +5072,7 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>12</v>
       </c>
@@ -5141,7 +5140,7 @@
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
-    <row r="28" spans="1:32" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>12</v>
       </c>
@@ -5217,7 +5216,7 @@
       </c>
       <c r="AF28" s="11"/>
     </row>
-    <row r="29" spans="1:32" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>12</v>
       </c>
@@ -5291,7 +5290,7 @@
       <c r="AE29" s="11"/>
       <c r="AF29" s="11"/>
     </row>
-    <row r="30" spans="1:32" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>12</v>
       </c>
@@ -5441,7 +5440,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:32" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>12</v>
       </c>
@@ -5682,7 +5681,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>12</v>
       </c>
@@ -5760,7 +5759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>12</v>
       </c>
@@ -5826,7 +5825,7 @@
       <c r="AE36" s="11"/>
       <c r="AF36" s="11"/>
     </row>
-    <row r="37" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>12</v>
       </c>
@@ -5904,7 +5903,7 @@
       </c>
       <c r="AF37" s="11"/>
     </row>
-    <row r="38" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>12</v>
       </c>
@@ -5980,7 +5979,7 @@
       <c r="AE38" s="11"/>
       <c r="AF38" s="11"/>
     </row>
-    <row r="39" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>12</v>
       </c>
@@ -6048,7 +6047,7 @@
       <c r="AE39" s="11"/>
       <c r="AF39" s="11"/>
     </row>
-    <row r="40" spans="1:33" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>12</v>
       </c>
@@ -6116,7 +6115,7 @@
       <c r="AE40" s="11"/>
       <c r="AF40" s="11"/>
     </row>
-    <row r="41" spans="1:33" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>12</v>
       </c>
@@ -6192,7 +6191,7 @@
       </c>
       <c r="AF41" s="11"/>
     </row>
-    <row r="42" spans="1:33" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>12</v>
       </c>
@@ -6266,7 +6265,7 @@
       <c r="AE42" s="11"/>
       <c r="AF42" s="11"/>
     </row>
-    <row r="43" spans="1:33" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>12</v>
       </c>
@@ -6416,7 +6415,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:33" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>12</v>
       </c>
@@ -6656,7 +6655,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:33" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>12</v>
       </c>
@@ -6734,7 +6733,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:32" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>12</v>
       </c>
@@ -6802,7 +6801,7 @@
       <c r="AE49" s="11"/>
       <c r="AF49" s="11"/>
     </row>
-    <row r="50" spans="1:32" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>12</v>
       </c>
@@ -6880,7 +6879,7 @@
       </c>
       <c r="AF50" s="11"/>
     </row>
-    <row r="51" spans="1:32" s="14" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>12</v>
       </c>
@@ -6956,7 +6955,7 @@
       <c r="AE51" s="11"/>
       <c r="AF51" s="11"/>
     </row>
-    <row r="52" spans="1:32" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>12</v>
       </c>
@@ -7024,7 +7023,7 @@
       <c r="AE52" s="11"/>
       <c r="AF52" s="11"/>
     </row>
-    <row r="53" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>12</v>
       </c>
@@ -7100,7 +7099,7 @@
       </c>
       <c r="AF53" s="3"/>
     </row>
-    <row r="54" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>12</v>
       </c>
@@ -7174,7 +7173,7 @@
       <c r="AE54" s="3"/>
       <c r="AF54" s="3"/>
     </row>
-    <row r="55" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>12</v>
       </c>
@@ -7324,7 +7323,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>12</v>
       </c>
@@ -7564,7 +7563,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>12</v>
       </c>
@@ -7642,7 +7641,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>12</v>
       </c>
@@ -7710,7 +7709,7 @@
       <c r="AE61" s="3"/>
       <c r="AF61" s="3"/>
     </row>
-    <row r="62" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>12</v>
       </c>
@@ -7788,7 +7787,7 @@
       </c>
       <c r="AF62" s="3"/>
     </row>
-    <row r="63" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>12</v>
       </c>
@@ -7864,7 +7863,7 @@
       <c r="AE63" s="3"/>
       <c r="AF63" s="3"/>
     </row>
-    <row r="64" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
         <v>12</v>
       </c>
@@ -7932,7 +7931,7 @@
       <c r="AE64" s="3"/>
       <c r="AF64" s="3"/>
     </row>
-    <row r="65" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>12</v>
       </c>
@@ -8008,7 +8007,7 @@
       </c>
       <c r="AF65" s="3"/>
     </row>
-    <row r="66" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>12</v>
       </c>
@@ -8082,7 +8081,7 @@
       <c r="AE66" s="3"/>
       <c r="AF66" s="3"/>
     </row>
-    <row r="67" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>12</v>
       </c>
@@ -8230,7 +8229,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>12</v>
       </c>
@@ -8469,7 +8468,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>12</v>
       </c>
@@ -8543,7 +8542,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>12</v>
       </c>
@@ -8611,7 +8610,7 @@
       <c r="AE73" s="3"/>
       <c r="AF73" s="3"/>
     </row>
-    <row r="74" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>12</v>
       </c>
@@ -8689,7 +8688,7 @@
       </c>
       <c r="AF74" s="3"/>
     </row>
-    <row r="75" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>12</v>
       </c>
@@ -8757,7 +8756,7 @@
       <c r="AE75" s="3"/>
       <c r="AF75" s="3"/>
     </row>
-    <row r="76" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>12</v>
       </c>
@@ -8833,7 +8832,7 @@
       </c>
       <c r="AF76" s="3"/>
     </row>
-    <row r="77" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>12</v>
       </c>
@@ -8907,7 +8906,7 @@
       <c r="AE77" s="3"/>
       <c r="AF77" s="3"/>
     </row>
-    <row r="78" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>12</v>
       </c>
@@ -9055,7 +9054,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>12</v>
       </c>
@@ -9294,7 +9293,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>12</v>
       </c>
@@ -9372,7 +9371,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>12</v>
       </c>
@@ -9440,7 +9439,7 @@
       <c r="AE84" s="3"/>
       <c r="AF84" s="3"/>
     </row>
-    <row r="85" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>12</v>
       </c>
@@ -9518,7 +9517,7 @@
       </c>
       <c r="AF85" s="3"/>
     </row>
-    <row r="86" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>12</v>
       </c>
@@ -9586,7 +9585,7 @@
       <c r="AE86" s="3"/>
       <c r="AF86" s="3"/>
     </row>
-    <row r="87" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>12</v>
       </c>
@@ -9662,7 +9661,7 @@
       </c>
       <c r="AF87" s="3"/>
     </row>
-    <row r="88" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>12</v>
       </c>
@@ -9736,7 +9735,7 @@
       <c r="AE88" s="3"/>
       <c r="AF88" s="3"/>
     </row>
-    <row r="89" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>12</v>
       </c>
@@ -9884,7 +9883,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="91" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>12</v>
       </c>
@@ -10125,7 +10124,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>12</v>
       </c>
@@ -10203,7 +10202,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>12</v>
       </c>
@@ -10271,7 +10270,7 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
     </row>
-    <row r="96" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>12</v>
       </c>
@@ -10349,7 +10348,7 @@
       </c>
       <c r="AF96" s="3"/>
     </row>
-    <row r="97" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>12</v>
       </c>
@@ -10417,7 +10416,7 @@
       <c r="AE97" s="3"/>
       <c r="AF97" s="3"/>
     </row>
-    <row r="98" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>12</v>
       </c>
@@ -10493,7 +10492,7 @@
       </c>
       <c r="AF98" s="3"/>
     </row>
-    <row r="99" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>12</v>
       </c>
@@ -10567,7 +10566,7 @@
       <c r="AE99" s="3"/>
       <c r="AF99" s="3"/>
     </row>
-    <row r="100" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>12</v>
       </c>
@@ -10715,7 +10714,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="102" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>12</v>
       </c>
@@ -10954,7 +10953,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>12</v>
       </c>
@@ -11032,7 +11031,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>12</v>
       </c>
@@ -11100,7 +11099,7 @@
       <c r="AE106" s="3"/>
       <c r="AF106" s="3"/>
     </row>
-    <row r="107" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>12</v>
       </c>
@@ -11178,7 +11177,7 @@
       </c>
       <c r="AF107" s="3"/>
     </row>
-    <row r="108" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>12</v>
       </c>
@@ -11246,7 +11245,7 @@
       <c r="AE108" s="3"/>
       <c r="AF108" s="3"/>
     </row>
-    <row r="109" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>12</v>
       </c>
@@ -11322,7 +11321,7 @@
       </c>
       <c r="AF109" s="3"/>
     </row>
-    <row r="110" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>12</v>
       </c>
@@ -11396,7 +11395,7 @@
       <c r="AE110" s="3"/>
       <c r="AF110" s="3"/>
     </row>
-    <row r="111" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>12</v>
       </c>
@@ -11544,7 +11543,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="113" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>12</v>
       </c>
@@ -11783,7 +11782,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="116" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>12</v>
       </c>
@@ -11861,7 +11860,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="117" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>12</v>
       </c>
@@ -11929,7 +11928,7 @@
       <c r="AE117" s="3"/>
       <c r="AF117" s="3"/>
     </row>
-    <row r="118" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>12</v>
       </c>
@@ -12007,7 +12006,7 @@
       </c>
       <c r="AF118" s="3"/>
     </row>
-    <row r="119" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>12</v>
       </c>
@@ -12075,7 +12074,7 @@
       <c r="AE119" s="3"/>
       <c r="AF119" s="3"/>
     </row>
-    <row r="120" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>12</v>
       </c>
@@ -12151,7 +12150,7 @@
       </c>
       <c r="AF120" s="3"/>
     </row>
-    <row r="121" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>12</v>
       </c>
@@ -12225,7 +12224,7 @@
       <c r="AE121" s="3"/>
       <c r="AF121" s="3"/>
     </row>
-    <row r="122" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>12</v>
       </c>
@@ -12373,7 +12372,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="124" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>12</v>
       </c>
@@ -12612,7 +12611,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>12</v>
       </c>
@@ -12690,7 +12689,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>12</v>
       </c>
@@ -12758,7 +12757,7 @@
       <c r="AE128" s="3"/>
       <c r="AF128" s="3"/>
     </row>
-    <row r="129" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>12</v>
       </c>
@@ -12836,7 +12835,7 @@
       </c>
       <c r="AF129" s="3"/>
     </row>
-    <row r="130" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>12</v>
       </c>
@@ -12904,7 +12903,7 @@
       <c r="AE130" s="3"/>
       <c r="AF130" s="3"/>
     </row>
-    <row r="131" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>12</v>
       </c>
@@ -12980,7 +12979,7 @@
       </c>
       <c r="AF131" s="3"/>
     </row>
-    <row r="132" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>12</v>
       </c>
@@ -13054,7 +13053,7 @@
       <c r="AE132" s="3"/>
       <c r="AF132" s="3"/>
     </row>
-    <row r="133" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>12</v>
       </c>
@@ -13202,7 +13201,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="135" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>12</v>
       </c>
@@ -13441,7 +13440,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>12</v>
       </c>
@@ -13519,7 +13518,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>12</v>
       </c>
@@ -13587,7 +13586,7 @@
       <c r="AE139" s="3"/>
       <c r="AF139" s="3"/>
     </row>
-    <row r="140" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>12</v>
       </c>
@@ -13665,7 +13664,7 @@
       </c>
       <c r="AF140" s="3"/>
     </row>
-    <row r="141" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>12</v>
       </c>
@@ -13733,7 +13732,7 @@
       <c r="AE141" s="3"/>
       <c r="AF141" s="3"/>
     </row>
-    <row r="142" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>12</v>
       </c>
@@ -13809,7 +13808,7 @@
       </c>
       <c r="AF142" s="3"/>
     </row>
-    <row r="143" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>12</v>
       </c>
@@ -13883,7 +13882,7 @@
       <c r="AE143" s="3"/>
       <c r="AF143" s="3"/>
     </row>
-    <row r="144" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>12</v>
       </c>
@@ -14031,7 +14030,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="146" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>12</v>
       </c>
@@ -14270,7 +14269,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>12</v>
       </c>
@@ -14348,7 +14347,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>12</v>
       </c>
@@ -14416,7 +14415,7 @@
       <c r="AE150" s="3"/>
       <c r="AF150" s="3"/>
     </row>
-    <row r="151" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>12</v>
       </c>
@@ -14494,7 +14493,7 @@
       </c>
       <c r="AF151" s="3"/>
     </row>
-    <row r="152" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>12</v>
       </c>
@@ -14562,7 +14561,7 @@
       <c r="AE152" s="3"/>
       <c r="AF152" s="3"/>
     </row>
-    <row r="153" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>12</v>
       </c>
@@ -14622,7 +14621,7 @@
       <c r="AE153" s="3"/>
       <c r="AF153" s="3"/>
     </row>
-    <row r="154" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>12</v>
       </c>
@@ -14698,7 +14697,7 @@
       </c>
       <c r="AF154" s="3"/>
     </row>
-    <row r="155" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>12</v>
       </c>
@@ -14772,7 +14771,7 @@
       <c r="AE155" s="3"/>
       <c r="AF155" s="3"/>
     </row>
-    <row r="156" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>12</v>
       </c>
@@ -14850,7 +14849,7 @@
       </c>
       <c r="AF156" s="3"/>
     </row>
-    <row r="157" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>12</v>
       </c>
@@ -15168,7 +15167,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>12</v>
       </c>
@@ -15246,7 +15245,7 @@
       </c>
       <c r="AF161" s="3"/>
     </row>
-    <row r="162" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>12</v>
       </c>
@@ -15314,7 +15313,7 @@
       <c r="AE162" s="3"/>
       <c r="AF162" s="3"/>
     </row>
-    <row r="163" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>12</v>
       </c>
@@ -15382,7 +15381,7 @@
       <c r="AE163" s="3"/>
       <c r="AF163" s="3"/>
     </row>
-    <row r="164" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>12</v>
       </c>
@@ -15450,7 +15449,7 @@
       <c r="AE164" s="3"/>
       <c r="AF164" s="3"/>
     </row>
-    <row r="165" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>12</v>
       </c>
@@ -15522,7 +15521,7 @@
       <c r="AE165" s="3"/>
       <c r="AF165" s="3"/>
     </row>
-    <row r="166" spans="1:32" s="10" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:32" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>12</v>
       </c>
@@ -15590,7 +15589,7 @@
       <c r="AE166" s="3"/>
       <c r="AF166" s="3"/>
     </row>
-    <row r="167" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>12</v>
       </c>
@@ -15658,7 +15657,7 @@
       <c r="AE167" s="3"/>
       <c r="AF167" s="3"/>
     </row>
-    <row r="168" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>12</v>
       </c>
@@ -15726,7 +15725,7 @@
       <c r="AE168" s="3"/>
       <c r="AF168" s="3"/>
     </row>
-    <row r="169" spans="1:32" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:32" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>12</v>
       </c>
@@ -15794,7 +15793,7 @@
       <c r="AE169" s="3"/>
       <c r="AF169" s="3"/>
     </row>
-    <row r="170" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>12</v>
       </c>
@@ -15872,7 +15871,7 @@
       </c>
       <c r="AF170" s="3"/>
     </row>
-    <row r="171" spans="1:32" s="10" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:32" s="10" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>12</v>
       </c>
@@ -15948,7 +15947,7 @@
       </c>
       <c r="AF171" s="3"/>
     </row>
-    <row r="172" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>12</v>
       </c>
@@ -16016,7 +16015,7 @@
       <c r="AE172" s="3"/>
       <c r="AF172" s="3"/>
     </row>
-    <row r="173" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>12</v>
       </c>
@@ -16092,7 +16091,7 @@
       </c>
       <c r="AF173" s="3"/>
     </row>
-    <row r="174" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>12</v>
       </c>
@@ -16166,7 +16165,7 @@
       <c r="AE174" s="3"/>
       <c r="AF174" s="3"/>
     </row>
-    <row r="175" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>12</v>
       </c>
@@ -16244,7 +16243,7 @@
       </c>
       <c r="AF175" s="3"/>
     </row>
-    <row r="176" spans="1:32" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>12</v>
       </c>
@@ -16565,7 +16564,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="180" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>12</v>
       </c>
@@ -16637,7 +16636,7 @@
       <c r="AE180" s="3"/>
       <c r="AF180" s="3"/>
     </row>
-    <row r="181" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>12</v>
       </c>
@@ -16705,7 +16704,7 @@
       <c r="AE181" s="3"/>
       <c r="AF181" s="3"/>
     </row>
-    <row r="182" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>12</v>
       </c>
@@ -16773,7 +16772,7 @@
       <c r="AE182" s="3"/>
       <c r="AF182" s="3"/>
     </row>
-    <row r="183" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>12</v>
       </c>
@@ -16841,7 +16840,7 @@
       <c r="AE183" s="3"/>
       <c r="AF183" s="3"/>
     </row>
-    <row r="184" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>12</v>
       </c>
@@ -16913,7 +16912,7 @@
       <c r="AE184" s="3"/>
       <c r="AF184" s="3"/>
     </row>
-    <row r="185" spans="1:33" s="10" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>12</v>
       </c>
@@ -16981,7 +16980,7 @@
       <c r="AE185" s="3"/>
       <c r="AF185" s="3"/>
     </row>
-    <row r="186" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>12</v>
       </c>
@@ -17049,7 +17048,7 @@
       <c r="AE186" s="3"/>
       <c r="AF186" s="3"/>
     </row>
-    <row r="187" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>12</v>
       </c>
@@ -17117,7 +17116,7 @@
       <c r="AE187" s="3"/>
       <c r="AF187" s="3"/>
     </row>
-    <row r="188" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>12</v>
       </c>
@@ -17185,7 +17184,7 @@
       <c r="AE188" s="3"/>
       <c r="AF188" s="3"/>
     </row>
-    <row r="189" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>12</v>
       </c>
@@ -17263,7 +17262,7 @@
       </c>
       <c r="AF189" s="3"/>
     </row>
-    <row r="190" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>12</v>
       </c>
@@ -17341,7 +17340,7 @@
       </c>
       <c r="AF190" s="3"/>
     </row>
-    <row r="191" spans="1:33" s="10" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>12</v>
       </c>
@@ -17419,7 +17418,7 @@
       </c>
       <c r="AF191" s="3"/>
     </row>
-    <row r="192" spans="1:33" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>12</v>
       </c>
@@ -17488,13 +17487,7 @@
       <c r="AF192" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF192" xr:uid="{3B918A07-AF31-4E8A-BA7B-30C90C452F60}">
-    <filterColumn colId="22">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AF192" xr:uid="{3B918A07-AF31-4E8A-BA7B-30C90C452F60}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="L2" r:id="rId1" xr:uid="{19A50234-077B-48E4-A86C-9A419CC7B586}"/>
